--- a/Result/profitability/6581.xlsx
+++ b/Result/profitability/6581.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM43"/>
+  <dimension ref="A1:AM44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5891,6 +5891,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6581</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>847</v>
+      </c>
+      <c r="D44" t="n">
+        <v>330</v>
+      </c>
+      <c r="E44" t="n">
+        <v>517</v>
+      </c>
+      <c r="F44" t="n">
+        <v>61</v>
+      </c>
+      <c r="G44" t="n">
+        <v>447</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>52.74%</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>442</v>
+      </c>
+      <c r="K44" t="n">
+        <v>356</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.785</v>
+      </c>
+      <c r="N44" t="n">
+        <v>52.93375</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.735042735042736</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>7.950000000000003</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.1498586239396795</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.7021276595744683</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>8.219999999999999</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.1557408109132248</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
